--- a/Naming Range.xlsx
+++ b/Naming Range.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9BDCE8A-7BB6-45CE-9496-67590229A792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CD859E-3A6D-4814-871C-E62B2FE81D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{24CE2151-FC2E-4A56-954F-BAEE307E7682}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="name">Sheet1!$A$2:$A$14</definedName>
+    <definedName name="salary">Sheet1!$B$2:$B$14</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,10 +37,105 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>Anjali Thakur</t>
+  </si>
+  <si>
+    <t>Anjum Chopra</t>
+  </si>
+  <si>
+    <t>Anupam Mishra</t>
+  </si>
+  <si>
+    <t>Arjun Jain</t>
+  </si>
+  <si>
+    <t>Arjun Kapoor</t>
+  </si>
+  <si>
+    <t>Ashwini</t>
+  </si>
+  <si>
+    <t>Jharna Biswal</t>
+  </si>
+  <si>
+    <t>JP Kumar</t>
+  </si>
+  <si>
+    <t>Manish Grover</t>
+  </si>
+  <si>
+    <t>Manisha Guha</t>
+  </si>
+  <si>
+    <t>Prakash Dutta</t>
+  </si>
+  <si>
+    <t>Prateek Babbar</t>
+  </si>
+  <si>
+    <t>Priya Agarwal</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -64,8 +163,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,9 +480,264 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CCFC-EA55-4AAC-AA47-1D2673F395C9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>16250</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <f>SUM(B2:B14)</f>
+        <v>131175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>6400</v>
+      </c>
+      <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7">
+        <f>AVERAGE(B2:B14)</f>
+        <v>10090.384615384615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>4500</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8">
+        <f>MAX(B2:B14)</f>
+        <v>16250</v>
+      </c>
+      <c r="L8" cm="1">
+        <f t="array" ref="L8:L20">salary</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>6275</v>
+      </c>
+      <c r="I9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9">
+        <f>MIN(B2:B14)</f>
+        <v>4500</v>
+      </c>
+      <c r="L9">
+        <v>12000</v>
+      </c>
+      <c r="P9" t="str" cm="1">
+        <f t="array" ref="P9:P21">name</f>
+        <v>Anjali Thakur</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>6250</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10">
+        <f>COUNT(B2:B14)</f>
+        <v>13</v>
+      </c>
+      <c r="L10">
+        <v>11250</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Anjum Chopra</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>8750</v>
+      </c>
+      <c r="L11">
+        <v>12000</v>
+      </c>
+      <c r="P11" t="str">
+        <v>Anupam Mishra</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>11250</v>
+      </c>
+      <c r="L12">
+        <v>16250</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Arjun Jain</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>10000</v>
+      </c>
+      <c r="L13">
+        <v>6400</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Arjun Kapoor</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>16250</v>
+      </c>
+      <c r="L14">
+        <v>4500</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Ashwini</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L15">
+        <v>6275</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Jharna Biswal</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="L16">
+        <v>6250</v>
+      </c>
+      <c r="P16" t="str">
+        <v>JP Kumar</v>
+      </c>
+    </row>
+    <row r="17" spans="12:16" x14ac:dyDescent="0.35">
+      <c r="L17">
+        <v>8750</v>
+      </c>
+      <c r="P17" t="str">
+        <v>Manish Grover</v>
+      </c>
+    </row>
+    <row r="18" spans="12:16" x14ac:dyDescent="0.35">
+      <c r="L18">
+        <v>11250</v>
+      </c>
+      <c r="P18" t="str">
+        <v>Manisha Guha</v>
+      </c>
+    </row>
+    <row r="19" spans="12:16" x14ac:dyDescent="0.35">
+      <c r="L19">
+        <v>10000</v>
+      </c>
+      <c r="P19" t="str">
+        <v>Prakash Dutta</v>
+      </c>
+    </row>
+    <row r="20" spans="12:16" x14ac:dyDescent="0.35">
+      <c r="L20">
+        <v>16250</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Prateek Babbar</v>
+      </c>
+    </row>
+    <row r="21" spans="12:16" x14ac:dyDescent="0.35">
+      <c r="P21" t="str">
+        <v>Priya Agarwal</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="custom" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B14" xr:uid="{8A39606C-B604-435B-84DA-A08869483B8B}">
+      <formula1>ISNUMBER(B2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A14" xr:uid="{FE408D2D-D19A-4765-B26C-B75A652C47CD}">
+      <formula1>ISTEXT(A1)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>